--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488121_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488121_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9086</v>
+        <v>5.5905</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2113</v>
+        <v>3.9493</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6974</v>
+        <v>1.6412</v>
       </c>
       <c r="G2" t="n">
         <v>1.8943</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8773</v>
+        <v>1.5592</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6689</v>
+        <v>1.407</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2084</v>
+        <v>0.1522</v>
       </c>
       <c r="V2" t="n">
         <v>0.7494</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3832</v>
+        <v>3.4715</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2932</v>
+        <v>3.5781</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09</v>
+        <v>-0.1066</v>
       </c>
       <c r="G3" t="n">
         <v>0.8080000000000001</v>
@@ -688,13 +688,13 @@
         <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8212</v>
+        <v>0.2671</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9762999999999999</v>
+        <v>0.3085</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1551</v>
+        <v>-0.0415</v>
       </c>
       <c r="V3" t="n">
         <v>1.2071</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0431</v>
+        <v>1.5468</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9162</v>
+        <v>1.9332</v>
       </c>
       <c r="F4" t="n">
-        <v>1.127</v>
+        <v>-0.3865</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2875</v>
+        <v>-1.0035</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8671</v>
+        <v>-0.5177</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5796</v>
+        <v>-0.4858</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7060999999999999</v>
+        <v>1.7776</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5454</v>
+        <v>2.0316</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1607</v>
+        <v>-0.254</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9936</v>
+        <v>-2.781</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4124</v>
+        <v>-2.5493</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4189</v>
+        <v>-0.2317</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1893</v>
+        <v>-2.1805</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3876</v>
+        <v>2.5769</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4694</v>
+        <v>1.0674</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7364</v>
+        <v>1.129</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7329</v>
+        <v>-0.0616</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.337</v>
+        <v>1.0864</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.337</v>
+        <v>1.2071</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. PAÑOS HUERTAS</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2053</v>
+        <v>1.4247</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2053</v>
+        <v>2.429</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-1.0042</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2053</v>
+        <v>0.1944</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.5044</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2053</v>
+        <v>-0.31</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2053</v>
+        <v>2.7758</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.0449</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2053</v>
+        <v>0.731</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-2.5814</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.5404</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.041</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.4809</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.3599</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7494</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.7243000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. PANOS HUERTAS</t>
+          <t>L. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0397</v>
+        <v>1.2053</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0701</v>
+        <v>1.2053</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9696</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6502</v>
+        <v>1.2053</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6915</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3417</v>
+        <v>1.2053</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8</v>
+        <v>1.2053</v>
       </c>
       <c r="K6" t="n">
-        <v>1.157</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.957</v>
+        <v>1.2053</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8502999999999999</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4656</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3847</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9743000000000001</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1042</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. CALDERON QUINONES</t>
+          <t>L. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9123</v>
+        <v>1.152</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1866</v>
+        <v>0.0701</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7257</v>
+        <v>1.0819</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6565</v>
+        <v>-1.6502</v>
       </c>
       <c r="H7" t="n">
-        <v>0.249</v>
+        <v>0.6915</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4075</v>
+        <v>-2.3417</v>
       </c>
       <c r="J7" t="n">
-        <v>0.249</v>
+        <v>-0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.249</v>
+        <v>1.157</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.957</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4075</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.4656</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4075</v>
+        <v>-0.3847</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>1.9822</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1982</v>
+        <v>1.9822</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0576</v>
+        <v>1.0866</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0624</v>
+        <v>0.8701</v>
       </c>
       <c r="U7" t="n">
-        <v>0.12</v>
+        <v>0.2165</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>R. CALDERON QUINONES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7802</v>
+        <v>0.93</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8967</v>
+        <v>0.2885</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1165</v>
+        <v>0.6415</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1944</v>
+        <v>0.6565</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5044</v>
+        <v>0.249</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.31</v>
+        <v>0.4075</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7758</v>
+        <v>0.249</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0449</v>
+        <v>0.249</v>
       </c>
       <c r="L8" t="n">
-        <v>0.731</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5814</v>
+        <v>0.4075</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5404</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.041</v>
+        <v>0.4075</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1805</v>
+        <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1637</v>
+        <v>0.0752</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1724</v>
+        <v>0.0395</v>
       </c>
       <c r="U8" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0358</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7494</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7243000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5019</v>
+        <v>0.9255</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1972</v>
+        <v>0.1636</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6953</v>
+        <v>0.7619</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0035</v>
+        <v>-0.2875</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5177</v>
+        <v>-0.8671</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4858</v>
+        <v>0.5796</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7776</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0316</v>
+        <v>0.5454</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.254</v>
+        <v>0.1607</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.781</v>
+        <v>-0.9936</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5493</v>
+        <v>-1.4124</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2317</v>
+        <v>0.4189</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1805</v>
+        <v>-1.1893</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5769</v>
+        <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0225</v>
+        <v>1.3518</v>
       </c>
       <c r="T9" t="n">
-        <v>0.393</v>
+        <v>0.9839</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3705</v>
+        <v>0.3679</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0864</v>
+        <v>-0.337</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2071</v>
+        <v>-0.337</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4651</v>
+        <v>0.6231</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0422</v>
+        <v>0.0596</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5073</v>
+        <v>0.5635</v>
       </c>
       <c r="G10" t="n">
         <v>0.4277</v>
@@ -1234,13 +1234,13 @@
         <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1608</v>
+        <v>-0.0028</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1406</v>
+        <v>-0.0191</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5603</v>
+        <v>-1.1299</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4197</v>
+        <v>1.1108</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0245</v>
@@ -1312,13 +1312,13 @@
         <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4694</v>
+        <v>0.591</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.121</v>
+        <v>0.3094</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5904</v>
+        <v>0.2816</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3873</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3076</v>
+        <v>-0.29</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0333</v>
+        <v>-0.9315</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7257</v>
+        <v>0.6415</v>
       </c>
       <c r="G12" t="n">
         <v>0.4277</v>
@@ -1390,13 +1390,13 @@
         <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0576</v>
+        <v>0.0752</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U12" t="n">
-        <v>0.12</v>
+        <v>0.0358</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7037</v>
+        <v>-0.5642</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4227</v>
+        <v>-1.5641</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7191</v>
+        <v>0.9999</v>
       </c>
       <c r="G13" t="n">
         <v>0.2966</v>
@@ -1468,13 +1468,13 @@
         <v>1.9822</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5764</v>
+        <v>0.7158</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8077</v>
+        <v>0.6664</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2313</v>
+        <v>0.0495</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3873</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.7728</v>
+        <v>-5.0576</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.5553</v>
+        <v>-2.0646</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2176</v>
+        <v>-2.9929</v>
       </c>
       <c r="G14" t="n">
         <v>-6.0517</v>
@@ -1546,13 +1546,13 @@
         <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1667</v>
+        <v>0.882</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4979</v>
+        <v>0.9885</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3312</v>
+        <v>-0.1065</v>
       </c>
       <c r="V14" t="n">
         <v>-1.4737</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.3147</v>
+        <v>10.9385</v>
       </c>
       <c r="E15" t="n">
-        <v>7.362800000000001</v>
+        <v>7.986600000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9521</v>
+        <v>2.952</v>
       </c>
       <c r="G15" t="n">
         <v>-3.1069</v>
@@ -1594,7 +1594,7 @@
         <v>0.9108000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.0178</v>
+        <v>-4.017799999999999</v>
       </c>
       <c r="J15" t="n">
         <v>10.0336</v>
@@ -1624,13 +1624,13 @@
         <v>18.8312</v>
       </c>
       <c r="S15" t="n">
-        <v>7.525499999999999</v>
+        <v>8.1494</v>
       </c>
       <c r="T15" t="n">
-        <v>6.517099999999999</v>
+        <v>7.141200000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0083</v>
+        <v>1.0085</v>
       </c>
       <c r="V15" t="n">
         <v>0.9404000000000003</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7825</v>
+        <v>2.4771</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5661</v>
+        <v>4.2418</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7836</v>
+        <v>-1.7647</v>
       </c>
       <c r="G16" t="n">
         <v>2.9924</v>
@@ -1702,13 +1702,13 @@
         <v>2.7751</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0833</v>
+        <v>-0.2221</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6668</v>
+        <v>0.3425</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5835</v>
+        <v>-0.5646</v>
       </c>
       <c r="V16" t="n">
         <v>-2.0772</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8718</v>
+        <v>1.0605</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7185</v>
+        <v>2.0241</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8466</v>
+        <v>-0.9635</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6192</v>
@@ -1858,13 +1858,13 @@
         <v>2.5769</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-0.7764</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6936</v>
+        <v>-0.388</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2715</v>
+        <v>-0.3884</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1207</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.801</v>
+        <v>1.021</v>
       </c>
       <c r="E19" t="n">
         <v>1.1444</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3435</v>
+        <v>-0.1234</v>
       </c>
       <c r="G19" t="n">
         <v>0.9452</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7478</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.623</v>
+        <v>-0.4029</v>
       </c>
       <c r="V19" t="n">
         <v>0.6036</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3888</v>
+        <v>-0.2588</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5433</v>
+        <v>-0.4414</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1545</v>
+        <v>0.1826</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5433</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1545</v>
+        <v>0.2845</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1358</v>
+        <v>0.2377</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6791</v>
+        <v>-0.4325</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6791</v>
+        <v>-0.6513</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.2188</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6791</v>
+        <v>1.1303</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-0.3677</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6791</v>
+        <v>1.498</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6791</v>
+        <v>2.3378</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.157</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6791</v>
+        <v>1.1807</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-1.2075</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-1.5247</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.3173</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.7751</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-1.3895</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.1613</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-1.2281</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.016</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1367</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7133</v>
+        <v>-0.6791</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2439</v>
+        <v>-0.6791</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4694</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1303</v>
+        <v>-0.6791</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3677</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1.498</v>
+        <v>-0.6791</v>
       </c>
       <c r="J22" t="n">
-        <v>2.3378</v>
+        <v>-0.6791</v>
       </c>
       <c r="K22" t="n">
-        <v>1.157</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1807</v>
+        <v>-0.6791</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2075</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5247</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3173</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7751</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6702</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2461</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.9164</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.016</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1367</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8269</v>
+        <v>-1.2039</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4882</v>
+        <v>-2.0807</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6613</v>
+        <v>0.8768</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4758</v>
@@ -2248,13 +2248,13 @@
         <v>2.3787</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7386</v>
+        <v>-0.1157</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3082</v>
+        <v>0.0993</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4304</v>
+        <v>-0.2149</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. LEGANOVIC</t>
+          <t>P. LOPEZ GOMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6925</v>
+        <v>-2.2661</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3749</v>
+        <v>-0.669</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3176</v>
+        <v>-1.5971</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5495</v>
+        <v>2.9775</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1369</v>
+        <v>1.248</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5874</v>
+        <v>1.7295</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0441</v>
+        <v>4.1322</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2.8387</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0441</v>
+        <v>1.2935</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5936</v>
+        <v>-1.1547</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1369</v>
+        <v>-1.5907</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5433</v>
+        <v>0.436</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.9822</v>
+        <v>-3.1716</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9822</v>
+        <v>-4.9556</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1608</v>
+        <v>-1.6143</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4368</v>
+        <v>-0.7157</v>
       </c>
       <c r="U24" t="n">
-        <v>0.276</v>
+        <v>-0.8986</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.4577</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>J. LEGANOVIC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,40 +2359,40 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1035</v>
+        <v>-2.3307</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8093</v>
+        <v>-2.0693</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2942</v>
+        <v>-0.2614</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5666</v>
+        <v>-0.5495</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.282</v>
+        <v>-1.1369</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7154</v>
+        <v>0.5874</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4579</v>
+        <v>0.0441</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6186</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1607</v>
+        <v>0.0441</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1087</v>
+        <v>-0.5936</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6634</v>
+        <v>-1.1369</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5547</v>
+        <v>0.5433</v>
       </c>
       <c r="P25" t="n">
         <v>-1.9822</v>
@@ -2404,28 +2404,28 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.24</v>
+        <v>0.201</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3047</v>
+        <v>-0.1312</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.3322</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.7947</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P. LOPEZ GOMEZ</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.1653</v>
+        <v>-3.431</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.0764</v>
+        <v>-1.8644</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.0888</v>
+        <v>-1.5666</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9775</v>
+        <v>-0.7128</v>
       </c>
       <c r="H26" t="n">
-        <v>1.248</v>
+        <v>-2.689</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7295</v>
+        <v>1.9762</v>
       </c>
       <c r="J26" t="n">
-        <v>4.1322</v>
+        <v>0.4554</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8387</v>
+        <v>-0.9547</v>
       </c>
       <c r="L26" t="n">
-        <v>1.2935</v>
+        <v>1.4101</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.1547</v>
+        <v>-1.1682</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.5907</v>
+        <v>-1.7343</v>
       </c>
       <c r="O26" t="n">
-        <v>0.436</v>
+        <v>0.5661</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.1716</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.9556</v>
+        <v>-3.9645</v>
       </c>
       <c r="R26" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.5135</v>
+        <v>-1.2298</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.1232</v>
+        <v>-0.166</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.3904</v>
+        <v>-1.0638</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.4577</v>
+        <v>0.8902</v>
       </c>
       <c r="W26" t="n">
-        <v>0.8701</v>
+        <v>1.8107</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.3278</v>
+        <v>-0.9204</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.4086</v>
+        <v>-3.4418</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.3737</v>
+        <v>-3.1149</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.0349</v>
+        <v>-0.3268</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.7128</v>
+        <v>-0.5666</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.689</v>
+        <v>-1.282</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9762</v>
+        <v>0.7154</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4554</v>
+        <v>-0.4579</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.9547</v>
+        <v>-0.6186</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4101</v>
+        <v>0.1607</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.1682</v>
+        <v>-0.1087</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.7343</v>
+        <v>-0.6634</v>
       </c>
       <c r="O27" t="n">
-        <v>0.5661</v>
+        <v>0.5547</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.3787</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3.9645</v>
+        <v>-1.9822</v>
       </c>
       <c r="R27" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.2073</v>
+        <v>-0.0982</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6753</v>
+        <v>-0.0009</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.532</v>
+        <v>-0.0974</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8902</v>
+        <v>-0.7947</v>
       </c>
       <c r="W27" t="n">
-        <v>1.8107</v>
+        <v>-0.674</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.9204</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="28">
@@ -2593,19 +2593,19 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-10.3147</v>
+        <v>-8.2773</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.951799999999999</v>
+        <v>-2.9518</v>
       </c>
       <c r="F28" t="n">
-        <v>-7.3628</v>
+        <v>-5.3253</v>
       </c>
       <c r="G28" t="n">
-        <v>3.1071</v>
+        <v>3.107100000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.9109000000000003</v>
+        <v>-0.9108999999999998</v>
       </c>
       <c r="I28" t="n">
         <v>4.018000000000001</v>
@@ -2629,7 +2629,7 @@
         <v>2.2655</v>
       </c>
       <c r="P28" t="n">
-        <v>-4.955500000000001</v>
+        <v>-4.9555</v>
       </c>
       <c r="Q28" t="n">
         <v>-18.8312</v>
@@ -2638,13 +2638,13 @@
         <v>13.8756</v>
       </c>
       <c r="S28" t="n">
-        <v>-7.525600000000001</v>
+        <v>-5.488200000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.0085</v>
+        <v>-1.0084</v>
       </c>
       <c r="U28" t="n">
-        <v>-6.517200000000001</v>
+        <v>-4.479700000000001</v>
       </c>
       <c r="V28" t="n">
         <v>-0.9405</v>
@@ -2653,7 +2653,7 @@
         <v>3.7471</v>
       </c>
       <c r="X28" t="n">
-        <v>-4.687499999999999</v>
+        <v>-4.6875</v>
       </c>
     </row>
   </sheetData>
